--- a/data/resultats_xlsx.xlsx
+++ b/data/resultats_xlsx.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1043" uniqueCount="303">
   <si>
     <t xml:space="preserve">EPREUVE</t>
   </si>
@@ -846,6 +846,78 @@
   </si>
   <si>
     <t xml:space="preserve">03:23.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01:45.49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04/10/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01:48.51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01:24.87</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:51.29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:56.91</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MALLAURAN Eva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:46.40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:51.43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:55.05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:37.43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:39.87</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:42.64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:42.77</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:44.38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:49.50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01:21.49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:45.56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01:17.01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:53.96</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:29.36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:33.94</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:39.84</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00:44.73</t>
   </si>
   <si>
     <t xml:space="preserve">NOM_PRENOM</t>
@@ -5880,25 +5952,25 @@
       </c>
     </row>
     <row r="176" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A176" s="0" t="s">
+      <c r="A176" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B176" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C176" s="0" t="s">
+      <c r="C176" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D176" s="0" t="n">
+      <c r="D176" s="1" t="n">
         <v>1983</v>
       </c>
-      <c r="E176" s="0" t="s">
+      <c r="E176" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="F176" s="4" t="s">
+      <c r="F176" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="G176" s="0" t="n">
+      <c r="G176" s="1" t="n">
         <v>943</v>
       </c>
       <c r="H176" s="1" t="str">
@@ -5907,25 +5979,25 @@
       </c>
     </row>
     <row r="177" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A177" s="0" t="s">
+      <c r="A177" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B177" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C177" s="0" t="s">
+      <c r="C177" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D177" s="0" t="n">
+      <c r="D177" s="1" t="n">
         <v>1978</v>
       </c>
-      <c r="E177" s="0" t="s">
+      <c r="E177" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="F177" s="4" t="s">
+      <c r="F177" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="G177" s="0" t="n">
+      <c r="G177" s="1" t="n">
         <v>835</v>
       </c>
       <c r="H177" s="1" t="str">
@@ -5934,25 +6006,25 @@
       </c>
     </row>
     <row r="178" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A178" s="0" t="s">
+      <c r="A178" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B178" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C178" s="0" t="s">
+      <c r="C178" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D178" s="0" t="n">
+      <c r="D178" s="1" t="n">
         <v>1996</v>
       </c>
-      <c r="E178" s="0" t="s">
+      <c r="E178" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="F178" s="4" t="s">
+      <c r="F178" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="G178" s="0" t="n">
+      <c r="G178" s="1" t="n">
         <v>612</v>
       </c>
       <c r="H178" s="1" t="str">
@@ -5961,25 +6033,25 @@
       </c>
     </row>
     <row r="179" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A179" s="0" t="s">
+      <c r="A179" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B179" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C179" s="0" t="s">
+      <c r="C179" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D179" s="0" t="n">
+      <c r="D179" s="1" t="n">
         <v>1967</v>
       </c>
-      <c r="E179" s="0" t="s">
+      <c r="E179" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="F179" s="4" t="s">
+      <c r="F179" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="G179" s="0" t="n">
+      <c r="G179" s="1" t="n">
         <v>655</v>
       </c>
       <c r="H179" s="1" t="str">
@@ -5988,25 +6060,25 @@
       </c>
     </row>
     <row r="180" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A180" s="0" t="s">
+      <c r="A180" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B180" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C180" s="0" t="s">
+      <c r="C180" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D180" s="0" t="n">
+      <c r="D180" s="1" t="n">
         <v>1979</v>
       </c>
-      <c r="E180" s="0" t="s">
+      <c r="E180" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="F180" s="4" t="s">
+      <c r="F180" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="G180" s="0" t="n">
+      <c r="G180" s="1" t="n">
         <v>590</v>
       </c>
       <c r="H180" s="1" t="str">
@@ -6015,25 +6087,25 @@
       </c>
     </row>
     <row r="181" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A181" s="0" t="s">
+      <c r="A181" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B181" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C181" s="0" t="s">
+      <c r="C181" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D181" s="0" t="n">
+      <c r="D181" s="1" t="n">
         <v>1983</v>
       </c>
-      <c r="E181" s="0" t="s">
+      <c r="E181" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="F181" s="4" t="s">
+      <c r="F181" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="G181" s="0" t="n">
+      <c r="G181" s="1" t="n">
         <v>766</v>
       </c>
       <c r="H181" s="1" t="str">
@@ -6042,25 +6114,25 @@
       </c>
     </row>
     <row r="182" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A182" s="0" t="s">
+      <c r="A182" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B182" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C182" s="0" t="s">
+      <c r="C182" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D182" s="0" t="n">
+      <c r="D182" s="1" t="n">
         <v>1996</v>
       </c>
-      <c r="E182" s="0" t="s">
+      <c r="E182" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="F182" s="4" t="s">
+      <c r="F182" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="G182" s="0" t="n">
+      <c r="G182" s="1" t="n">
         <v>475</v>
       </c>
       <c r="H182" s="1" t="str">
@@ -6069,25 +6141,25 @@
       </c>
     </row>
     <row r="183" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A183" s="0" t="s">
+      <c r="A183" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B183" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C183" s="0" t="s">
+      <c r="C183" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D183" s="0" t="n">
+      <c r="D183" s="1" t="n">
         <v>1967</v>
       </c>
-      <c r="E183" s="0" t="s">
+      <c r="E183" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="F183" s="4" t="s">
+      <c r="F183" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="G183" s="0" t="n">
+      <c r="G183" s="1" t="n">
         <v>484</v>
       </c>
       <c r="H183" s="1" t="str">
@@ -6096,25 +6168,25 @@
       </c>
     </row>
     <row r="184" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A184" s="0" t="s">
+      <c r="A184" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B184" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C184" s="0" t="s">
+      <c r="C184" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D184" s="0" t="n">
+      <c r="D184" s="1" t="n">
         <v>1973</v>
       </c>
-      <c r="E184" s="0" t="s">
+      <c r="E184" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="F184" s="4" t="s">
+      <c r="F184" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="G184" s="0" t="n">
+      <c r="G184" s="1" t="n">
         <v>451</v>
       </c>
       <c r="H184" s="1" t="str">
@@ -6123,25 +6195,25 @@
       </c>
     </row>
     <row r="185" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A185" s="0" t="s">
+      <c r="A185" s="1" t="s">
         <v>262</v>
       </c>
       <c r="B185" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C185" s="0" t="s">
+      <c r="C185" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D185" s="0" t="n">
+      <c r="D185" s="1" t="n">
         <v>1973</v>
       </c>
-      <c r="E185" s="0" t="s">
+      <c r="E185" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="F185" s="4" t="s">
+      <c r="F185" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="G185" s="0" t="n">
+      <c r="G185" s="1" t="n">
         <v>432</v>
       </c>
       <c r="H185" s="1" t="str">
@@ -6150,25 +6222,25 @@
       </c>
     </row>
     <row r="186" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A186" s="0" t="s">
+      <c r="A186" s="1" t="s">
         <v>248</v>
       </c>
       <c r="B186" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C186" s="0" t="s">
+      <c r="C186" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D186" s="0" t="n">
+      <c r="D186" s="1" t="n">
         <v>1993</v>
       </c>
-      <c r="E186" s="0" t="s">
+      <c r="E186" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="F186" s="4" t="s">
+      <c r="F186" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="G186" s="0" t="n">
+      <c r="G186" s="1" t="n">
         <v>654</v>
       </c>
       <c r="H186" s="1" t="str">
@@ -6177,25 +6249,25 @@
       </c>
     </row>
     <row r="187" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A187" s="0" t="s">
+      <c r="A187" s="1" t="s">
         <v>248</v>
       </c>
       <c r="B187" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C187" s="0" t="s">
+      <c r="C187" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D187" s="0" t="n">
+      <c r="D187" s="1" t="n">
         <v>1978</v>
       </c>
-      <c r="E187" s="0" t="s">
+      <c r="E187" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="F187" s="4" t="s">
+      <c r="F187" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="G187" s="0" t="n">
+      <c r="G187" s="1" t="n">
         <v>697</v>
       </c>
       <c r="H187" s="1" t="str">
@@ -6204,25 +6276,25 @@
       </c>
     </row>
     <row r="188" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A188" s="0" t="s">
+      <c r="A188" s="1" t="s">
         <v>248</v>
       </c>
       <c r="B188" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C188" s="0" t="s">
+      <c r="C188" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D188" s="0" t="n">
+      <c r="D188" s="1" t="n">
         <v>1996</v>
       </c>
-      <c r="E188" s="0" t="s">
+      <c r="E188" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="F188" s="4" t="s">
+      <c r="F188" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="G188" s="0" t="n">
+      <c r="G188" s="1" t="n">
         <v>524</v>
       </c>
       <c r="H188" s="1" t="str">
@@ -6231,25 +6303,25 @@
       </c>
     </row>
     <row r="189" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A189" s="0" t="s">
+      <c r="A189" s="1" t="s">
         <v>248</v>
       </c>
       <c r="B189" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C189" s="0" t="s">
+      <c r="C189" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D189" s="0" t="n">
+      <c r="D189" s="1" t="n">
         <v>1983</v>
       </c>
-      <c r="E189" s="0" t="s">
+      <c r="E189" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="F189" s="4" t="s">
+      <c r="F189" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="G189" s="0" t="n">
+      <c r="G189" s="1" t="n">
         <v>696</v>
       </c>
       <c r="H189" s="1" t="str">
@@ -6258,25 +6330,25 @@
       </c>
     </row>
     <row r="190" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A190" s="0" t="s">
+      <c r="A190" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B190" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C190" s="0" t="s">
+      <c r="C190" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D190" s="0" t="n">
+      <c r="D190" s="1" t="n">
         <v>1993</v>
       </c>
-      <c r="E190" s="0" t="s">
+      <c r="E190" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="F190" s="4" t="s">
+      <c r="F190" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="G190" s="0" t="n">
+      <c r="G190" s="1" t="n">
         <v>609</v>
       </c>
       <c r="H190" s="1" t="str">
@@ -6285,25 +6357,25 @@
       </c>
     </row>
     <row r="191" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A191" s="0" t="s">
+      <c r="A191" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B191" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C191" s="0" t="s">
+      <c r="C191" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D191" s="0" t="n">
+      <c r="D191" s="1" t="n">
         <v>1983</v>
       </c>
-      <c r="E191" s="0" t="s">
+      <c r="E191" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="F191" s="4" t="s">
+      <c r="F191" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="G191" s="0" t="n">
+      <c r="G191" s="1" t="n">
         <v>733</v>
       </c>
       <c r="H191" s="1" t="str">
@@ -6312,25 +6384,25 @@
       </c>
     </row>
     <row r="192" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A192" s="0" t="s">
+      <c r="A192" s="1" t="s">
         <v>270</v>
       </c>
       <c r="B192" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C192" s="0" t="s">
+      <c r="C192" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D192" s="0" t="n">
+      <c r="D192" s="1" t="n">
         <v>1993</v>
       </c>
-      <c r="E192" s="0" t="s">
+      <c r="E192" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="F192" s="4" t="s">
+      <c r="F192" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="G192" s="0" t="n">
+      <c r="G192" s="1" t="n">
         <v>476</v>
       </c>
       <c r="H192" s="1" t="str">
@@ -6339,25 +6411,25 @@
       </c>
     </row>
     <row r="193" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A193" s="0" t="s">
+      <c r="A193" s="1" t="s">
         <v>272</v>
       </c>
       <c r="B193" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C193" s="0" t="s">
+      <c r="C193" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D193" s="0" t="n">
+      <c r="D193" s="1" t="n">
         <v>1993</v>
       </c>
-      <c r="E193" s="0" t="s">
+      <c r="E193" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="F193" s="4" t="s">
+      <c r="F193" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="G193" s="0" t="n">
+      <c r="G193" s="1" t="n">
         <v>512</v>
       </c>
       <c r="H193" s="1" t="str">
@@ -6366,25 +6438,25 @@
       </c>
     </row>
     <row r="194" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A194" s="0" t="s">
+      <c r="A194" s="1" t="s">
         <v>272</v>
       </c>
       <c r="B194" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C194" s="0" t="s">
+      <c r="C194" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D194" s="0" t="n">
+      <c r="D194" s="1" t="n">
         <v>1996</v>
       </c>
-      <c r="E194" s="0" t="s">
+      <c r="E194" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="F194" s="4" t="s">
+      <c r="F194" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="G194" s="0" t="n">
+      <c r="G194" s="1" t="n">
         <v>358</v>
       </c>
       <c r="H194" s="1" t="str">
@@ -6392,6 +6464,628 @@
         <v>Master C1</v>
       </c>
     </row>
+    <row r="195" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A195" s="0" t="s">
+        <v>190</v>
+      </c>
+      <c r="B195" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C195" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="D195" s="0" t="n">
+        <v>2012</v>
+      </c>
+      <c r="E195" s="0" t="s">
+        <v>275</v>
+      </c>
+      <c r="F195" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="G195" s="0" t="n">
+        <v>533</v>
+      </c>
+      <c r="H195" s="1" t="str">
+        <f aca="false">IF((YEAR(F195)-D195)&lt;=11,"Avenirs",IF((YEAR(F195)-D195)&lt;=13,"Benjamins",IF((YEAR(F195)-D195)&lt;=18,"Juniors",IF((YEAR(F195)-D195)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F195)-D195-25)/5,0)))))</f>
+        <v>Juniors</v>
+      </c>
+    </row>
+    <row r="196" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A196" s="0" t="s">
+        <v>190</v>
+      </c>
+      <c r="B196" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C196" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="D196" s="0" t="n">
+        <v>2013</v>
+      </c>
+      <c r="E196" s="0" t="s">
+        <v>277</v>
+      </c>
+      <c r="F196" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="G196" s="0" t="n">
+        <v>485</v>
+      </c>
+      <c r="H196" s="1" t="str">
+        <f aca="false">IF((YEAR(F196)-D196)&lt;=11,"Avenirs",IF((YEAR(F196)-D196)&lt;=13,"Benjamins",IF((YEAR(F196)-D196)&lt;=18,"Juniors",IF((YEAR(F196)-D196)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F196)-D196-25)/5,0)))))</f>
+        <v>Benjamins</v>
+      </c>
+    </row>
+    <row r="197" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A197" s="0" t="s">
+        <v>131</v>
+      </c>
+      <c r="B197" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C197" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="D197" s="0" t="n">
+        <v>2013</v>
+      </c>
+      <c r="E197" s="0" t="s">
+        <v>278</v>
+      </c>
+      <c r="F197" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="G197" s="0" t="n">
+        <v>414</v>
+      </c>
+      <c r="H197" s="1" t="str">
+        <f aca="false">IF((YEAR(F197)-D197)&lt;=11,"Avenirs",IF((YEAR(F197)-D197)&lt;=13,"Benjamins",IF((YEAR(F197)-D197)&lt;=18,"Juniors",IF((YEAR(F197)-D197)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F197)-D197-25)/5,0)))))</f>
+        <v>Benjamins</v>
+      </c>
+    </row>
+    <row r="198" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A198" s="0" t="s">
+        <v>81</v>
+      </c>
+      <c r="B198" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C198" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="D198" s="0" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E198" s="0" t="s">
+        <v>279</v>
+      </c>
+      <c r="F198" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="G198" s="0" t="n">
+        <v>409</v>
+      </c>
+      <c r="H198" s="1" t="str">
+        <f aca="false">IF((YEAR(F198)-D198)&lt;=11,"Avenirs",IF((YEAR(F198)-D198)&lt;=13,"Benjamins",IF((YEAR(F198)-D198)&lt;=18,"Juniors",IF((YEAR(F198)-D198)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F198)-D198-25)/5,0)))))</f>
+        <v>Avenirs</v>
+      </c>
+    </row>
+    <row r="199" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A199" s="0" t="s">
+        <v>81</v>
+      </c>
+      <c r="B199" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C199" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="D199" s="0" t="n">
+        <v>2014</v>
+      </c>
+      <c r="E199" s="0" t="s">
+        <v>280</v>
+      </c>
+      <c r="F199" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="G199" s="0" t="n">
+        <v>249</v>
+      </c>
+      <c r="H199" s="1" t="str">
+        <f aca="false">IF((YEAR(F199)-D199)&lt;=11,"Avenirs",IF((YEAR(F199)-D199)&lt;=13,"Benjamins",IF((YEAR(F199)-D199)&lt;=18,"Juniors",IF((YEAR(F199)-D199)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F199)-D199-25)/5,0)))))</f>
+        <v>Benjamins</v>
+      </c>
+    </row>
+    <row r="200" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A200" s="0" t="s">
+        <v>110</v>
+      </c>
+      <c r="B200" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C200" s="0" t="s">
+        <v>281</v>
+      </c>
+      <c r="D200" s="0" t="n">
+        <v>2012</v>
+      </c>
+      <c r="E200" s="0" t="s">
+        <v>282</v>
+      </c>
+      <c r="F200" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="G200" s="0" t="n">
+        <v>441</v>
+      </c>
+      <c r="H200" s="1" t="str">
+        <f aca="false">IF((YEAR(F200)-D200)&lt;=11,"Avenirs",IF((YEAR(F200)-D200)&lt;=13,"Benjamins",IF((YEAR(F200)-D200)&lt;=18,"Juniors",IF((YEAR(F200)-D200)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F200)-D200-25)/5,0)))))</f>
+        <v>Juniors</v>
+      </c>
+    </row>
+    <row r="201" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A201" s="0" t="s">
+        <v>110</v>
+      </c>
+      <c r="B201" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C201" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="D201" s="0" t="n">
+        <v>2010</v>
+      </c>
+      <c r="E201" s="0" t="s">
+        <v>283</v>
+      </c>
+      <c r="F201" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="G201" s="0" t="n">
+        <v>285</v>
+      </c>
+      <c r="H201" s="1" t="str">
+        <f aca="false">IF((YEAR(F201)-D201)&lt;=11,"Avenirs",IF((YEAR(F201)-D201)&lt;=13,"Benjamins",IF((YEAR(F201)-D201)&lt;=18,"Juniors",IF((YEAR(F201)-D201)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F201)-D201-25)/5,0)))))</f>
+        <v>Juniors</v>
+      </c>
+    </row>
+    <row r="202" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A202" s="0" t="s">
+        <v>110</v>
+      </c>
+      <c r="B202" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C202" s="0" t="s">
+        <v>155</v>
+      </c>
+      <c r="D202" s="0" t="n">
+        <v>2016</v>
+      </c>
+      <c r="E202" s="0" t="s">
+        <v>284</v>
+      </c>
+      <c r="F202" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="G202" s="0" t="n">
+        <v>193</v>
+      </c>
+      <c r="H202" s="1" t="str">
+        <f aca="false">IF((YEAR(F202)-D202)&lt;=11,"Avenirs",IF((YEAR(F202)-D202)&lt;=13,"Benjamins",IF((YEAR(F202)-D202)&lt;=18,"Juniors",IF((YEAR(F202)-D202)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F202)-D202-25)/5,0)))))</f>
+        <v>Avenirs</v>
+      </c>
+    </row>
+    <row r="203" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A203" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="B203" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C203" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="D203" s="0" t="n">
+        <v>2012</v>
+      </c>
+      <c r="E203" s="0" t="s">
+        <v>285</v>
+      </c>
+      <c r="F203" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="G203" s="0" t="n">
+        <v>529</v>
+      </c>
+      <c r="H203" s="1" t="str">
+        <f aca="false">IF((YEAR(F203)-D203)&lt;=11,"Avenirs",IF((YEAR(F203)-D203)&lt;=13,"Benjamins",IF((YEAR(F203)-D203)&lt;=18,"Juniors",IF((YEAR(F203)-D203)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F203)-D203-25)/5,0)))))</f>
+        <v>Juniors</v>
+      </c>
+    </row>
+    <row r="204" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A204" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="B204" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C204" s="0" t="s">
+        <v>281</v>
+      </c>
+      <c r="D204" s="0" t="n">
+        <v>2012</v>
+      </c>
+      <c r="E204" s="0" t="s">
+        <v>286</v>
+      </c>
+      <c r="F204" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="G204" s="0" t="n">
+        <v>417</v>
+      </c>
+      <c r="H204" s="1" t="str">
+        <f aca="false">IF((YEAR(F204)-D204)&lt;=11,"Avenirs",IF((YEAR(F204)-D204)&lt;=13,"Benjamins",IF((YEAR(F204)-D204)&lt;=18,"Juniors",IF((YEAR(F204)-D204)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F204)-D204-25)/5,0)))))</f>
+        <v>Juniors</v>
+      </c>
+    </row>
+    <row r="205" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A205" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="B205" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C205" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="D205" s="0" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E205" s="0" t="s">
+        <v>287</v>
+      </c>
+      <c r="F205" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="G205" s="0" t="n">
+        <v>306</v>
+      </c>
+      <c r="H205" s="1" t="str">
+        <f aca="false">IF((YEAR(F205)-D205)&lt;=11,"Avenirs",IF((YEAR(F205)-D205)&lt;=13,"Benjamins",IF((YEAR(F205)-D205)&lt;=18,"Juniors",IF((YEAR(F205)-D205)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F205)-D205-25)/5,0)))))</f>
+        <v>Avenirs</v>
+      </c>
+    </row>
+    <row r="206" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A206" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="B206" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C206" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="D206" s="0" t="n">
+        <v>2014</v>
+      </c>
+      <c r="E206" s="0" t="s">
+        <v>288</v>
+      </c>
+      <c r="F206" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="G206" s="0" t="n">
+        <v>302</v>
+      </c>
+      <c r="H206" s="1" t="str">
+        <f aca="false">IF((YEAR(F206)-D206)&lt;=11,"Avenirs",IF((YEAR(F206)-D206)&lt;=13,"Benjamins",IF((YEAR(F206)-D206)&lt;=18,"Juniors",IF((YEAR(F206)-D206)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F206)-D206-25)/5,0)))))</f>
+        <v>Benjamins</v>
+      </c>
+    </row>
+    <row r="207" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A207" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="B207" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C207" s="0" t="s">
+        <v>155</v>
+      </c>
+      <c r="D207" s="0" t="n">
+        <v>2016</v>
+      </c>
+      <c r="E207" s="0" t="s">
+        <v>289</v>
+      </c>
+      <c r="F207" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="G207" s="0" t="n">
+        <v>245</v>
+      </c>
+      <c r="H207" s="1" t="str">
+        <f aca="false">IF((YEAR(F207)-D207)&lt;=11,"Avenirs",IF((YEAR(F207)-D207)&lt;=13,"Benjamins",IF((YEAR(F207)-D207)&lt;=18,"Juniors",IF((YEAR(F207)-D207)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F207)-D207-25)/5,0)))))</f>
+        <v>Avenirs</v>
+      </c>
+    </row>
+    <row r="208" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A208" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="B208" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C208" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="D208" s="0" t="n">
+        <v>2010</v>
+      </c>
+      <c r="E208" s="0" t="s">
+        <v>290</v>
+      </c>
+      <c r="F208" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="G208" s="0" t="n">
+        <v>209</v>
+      </c>
+      <c r="H208" s="1" t="str">
+        <f aca="false">IF((YEAR(F208)-D208)&lt;=11,"Avenirs",IF((YEAR(F208)-D208)&lt;=13,"Benjamins",IF((YEAR(F208)-D208)&lt;=18,"Juniors",IF((YEAR(F208)-D208)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F208)-D208-25)/5,0)))))</f>
+        <v>Juniors</v>
+      </c>
+    </row>
+    <row r="209" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A209" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="B209" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C209" s="0" t="s">
+        <v>125</v>
+      </c>
+      <c r="D209" s="0" t="n">
+        <v>2008</v>
+      </c>
+      <c r="E209" s="0" t="s">
+        <v>291</v>
+      </c>
+      <c r="F209" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="G209" s="0" t="n">
+        <v>570</v>
+      </c>
+      <c r="H209" s="1" t="str">
+        <f aca="false">IF((YEAR(F209)-D209)&lt;=11,"Avenirs",IF((YEAR(F209)-D209)&lt;=13,"Benjamins",IF((YEAR(F209)-D209)&lt;=18,"Juniors",IF((YEAR(F209)-D209)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F209)-D209-25)/5,0)))))</f>
+        <v>Juniors</v>
+      </c>
+    </row>
+    <row r="210" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A210" s="0" t="s">
+        <v>248</v>
+      </c>
+      <c r="B210" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C210" s="0" t="s">
+        <v>127</v>
+      </c>
+      <c r="D210" s="0" t="n">
+        <v>2012</v>
+      </c>
+      <c r="E210" s="0" t="s">
+        <v>292</v>
+      </c>
+      <c r="F210" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="G210" s="0" t="n">
+        <v>467</v>
+      </c>
+      <c r="H210" s="1" t="str">
+        <f aca="false">IF((YEAR(F210)-D210)&lt;=11,"Avenirs",IF((YEAR(F210)-D210)&lt;=13,"Benjamins",IF((YEAR(F210)-D210)&lt;=18,"Juniors",IF((YEAR(F210)-D210)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F210)-D210-25)/5,0)))))</f>
+        <v>Juniors</v>
+      </c>
+    </row>
+    <row r="211" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A211" s="0" t="s">
+        <v>248</v>
+      </c>
+      <c r="B211" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C211" s="0" t="s">
+        <v>161</v>
+      </c>
+      <c r="D211" s="0" t="n">
+        <v>2016</v>
+      </c>
+      <c r="E211" s="0" t="s">
+        <v>293</v>
+      </c>
+      <c r="F211" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="G211" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H211" s="1" t="str">
+        <f aca="false">IF((YEAR(F211)-D211)&lt;=11,"Avenirs",IF((YEAR(F211)-D211)&lt;=13,"Benjamins",IF((YEAR(F211)-D211)&lt;=18,"Juniors",IF((YEAR(F211)-D211)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F211)-D211-25)/5,0)))))</f>
+        <v>Avenirs</v>
+      </c>
+    </row>
+    <row r="212" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A212" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="B212" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C212" s="0" t="s">
+        <v>144</v>
+      </c>
+      <c r="D212" s="0" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E212" s="0" t="s">
+        <v>86</v>
+      </c>
+      <c r="F212" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="G212" s="0" t="n">
+        <v>129</v>
+      </c>
+      <c r="H212" s="1" t="str">
+        <f aca="false">IF((YEAR(F212)-D212)&lt;=11,"Avenirs",IF((YEAR(F212)-D212)&lt;=13,"Benjamins",IF((YEAR(F212)-D212)&lt;=18,"Juniors",IF((YEAR(F212)-D212)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F212)-D212-25)/5,0)))))</f>
+        <v>Avenirs</v>
+      </c>
+    </row>
+    <row r="213" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A213" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="B213" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C213" s="0" t="s">
+        <v>142</v>
+      </c>
+      <c r="D213" s="0" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E213" s="0" t="s">
+        <v>294</v>
+      </c>
+      <c r="F213" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="G213" s="0" t="n">
+        <v>112</v>
+      </c>
+      <c r="H213" s="1" t="str">
+        <f aca="false">IF((YEAR(F213)-D213)&lt;=11,"Avenirs",IF((YEAR(F213)-D213)&lt;=13,"Benjamins",IF((YEAR(F213)-D213)&lt;=18,"Juniors",IF((YEAR(F213)-D213)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F213)-D213-25)/5,0)))))</f>
+        <v>Avenirs</v>
+      </c>
+    </row>
+    <row r="214" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A214" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="B214" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C214" s="0" t="s">
+        <v>125</v>
+      </c>
+      <c r="D214" s="0" t="n">
+        <v>2008</v>
+      </c>
+      <c r="E214" s="0" t="s">
+        <v>295</v>
+      </c>
+      <c r="F214" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="G214" s="0" t="n">
+        <v>823</v>
+      </c>
+      <c r="H214" s="1" t="str">
+        <f aca="false">IF((YEAR(F214)-D214)&lt;=11,"Avenirs",IF((YEAR(F214)-D214)&lt;=13,"Benjamins",IF((YEAR(F214)-D214)&lt;=18,"Juniors",IF((YEAR(F214)-D214)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F214)-D214-25)/5,0)))))</f>
+        <v>Juniors</v>
+      </c>
+    </row>
+    <row r="215" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A215" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="B215" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C215" s="0" t="s">
+        <v>127</v>
+      </c>
+      <c r="D215" s="0" t="n">
+        <v>2012</v>
+      </c>
+      <c r="E215" s="0" t="s">
+        <v>296</v>
+      </c>
+      <c r="F215" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="G215" s="0" t="n">
+        <v>573</v>
+      </c>
+      <c r="H215" s="1" t="str">
+        <f aca="false">IF((YEAR(F215)-D215)&lt;=11,"Avenirs",IF((YEAR(F215)-D215)&lt;=13,"Benjamins",IF((YEAR(F215)-D215)&lt;=18,"Juniors",IF((YEAR(F215)-D215)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F215)-D215-25)/5,0)))))</f>
+        <v>Juniors</v>
+      </c>
+    </row>
+    <row r="216" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A216" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="B216" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C216" s="0" t="s">
+        <v>142</v>
+      </c>
+      <c r="D216" s="0" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E216" s="0" t="s">
+        <v>297</v>
+      </c>
+      <c r="F216" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="G216" s="0" t="n">
+        <v>317</v>
+      </c>
+      <c r="H216" s="1" t="str">
+        <f aca="false">IF((YEAR(F216)-D216)&lt;=11,"Avenirs",IF((YEAR(F216)-D216)&lt;=13,"Benjamins",IF((YEAR(F216)-D216)&lt;=18,"Juniors",IF((YEAR(F216)-D216)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F216)-D216-25)/5,0)))))</f>
+        <v>Avenirs</v>
+      </c>
+    </row>
+    <row r="217" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A217" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="B217" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C217" s="0" t="s">
+        <v>144</v>
+      </c>
+      <c r="D217" s="0" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E217" s="0" t="s">
+        <v>298</v>
+      </c>
+      <c r="F217" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="G217" s="0" t="n">
+        <v>162</v>
+      </c>
+      <c r="H217" s="1" t="str">
+        <f aca="false">IF((YEAR(F217)-D217)&lt;=11,"Avenirs",IF((YEAR(F217)-D217)&lt;=13,"Benjamins",IF((YEAR(F217)-D217)&lt;=18,"Juniors",IF((YEAR(F217)-D217)&lt;=25,"Seniors","Master C"&amp;ROUNDUP((YEAR(F217)-D217-25)/5,0)))))</f>
+        <v>Avenirs</v>
+      </c>
+    </row>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -6422,19 +7116,19 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>275</v>
+        <v>299</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>276</v>
+        <v>300</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>277</v>
+        <v>301</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>278</v>
+        <v>302</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
